--- a/training_result/90/0/c/parameters_4.xlsx
+++ b/training_result/90/0/c/parameters_4.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>29.6408</v>
+        <v>32.9054</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6283</v>
+        <v>0.6284999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.9536</v>
+        <v>-13.3715</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0265</v>
+        <v>1.0314</v>
       </c>
     </row>
     <row r="9">
@@ -547,7 +547,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>8.1944</v>
+        <v>19.0528</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2142</v>
+        <v>0.2141</v>
       </c>
     </row>
     <row r="12">
@@ -586,7 +586,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-35.9585</v>
+        <v>-29.2304</v>
       </c>
     </row>
     <row r="14">
@@ -625,7 +625,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>19.3723</v>
+        <v>23.7418</v>
       </c>
     </row>
     <row r="17">
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27.7422</v>
+        <v>10.3099</v>
       </c>
     </row>
     <row r="20">
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1083</v>
+        <v>0.1084</v>
       </c>
     </row>
     <row r="21">
@@ -703,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>16.6279</v>
+        <v>20.6802</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.5011</v>
       </c>
     </row>
     <row r="24">
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>27.9194</v>
+        <v>25.5839</v>
       </c>
     </row>
     <row r="26">
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>24.1561</v>
+        <v>22.3265</v>
       </c>
     </row>
     <row r="29">
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6161</v>
+        <v>0.6159</v>
       </c>
     </row>
     <row r="30">
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>-23.0693</v>
+        <v>-6.0758</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0498</v>
+        <v>-0.0568</v>
       </c>
     </row>
     <row r="33">
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>28.8666</v>
+        <v>20.8272</v>
       </c>
     </row>
     <row r="35">
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1.4344</v>
+        <v>1.4332</v>
       </c>
     </row>
     <row r="36">
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>22.9909</v>
+        <v>19.0398</v>
       </c>
     </row>
     <row r="38">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7052</v>
+        <v>0.7062</v>
       </c>
     </row>
     <row r="39">
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>17.5078</v>
+        <v>15.3932</v>
       </c>
     </row>
     <row r="41">
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1033</v>
+        <v>-0.1061</v>
       </c>
     </row>
     <row r="42">
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>-12.8407</v>
+        <v>-10.8091</v>
       </c>
     </row>
     <row r="44">
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0979</v>
+        <v>0.09710000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>-23.7033</v>
+        <v>-16.014</v>
       </c>
     </row>
     <row r="47">
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>2.8243</v>
+        <v>2.1266</v>
       </c>
     </row>
     <row r="50">
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5349</v>
+        <v>0.2025</v>
       </c>
     </row>
     <row r="53">
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1294</v>
+        <v>-0.1253</v>
       </c>
     </row>
     <row r="54">
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>-14.5923</v>
+        <v>-9.2034</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0451</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="57">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>10.5322</v>
+        <v>12.7117</v>
       </c>
     </row>
     <row r="59">
@@ -1184,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0578</v>
+        <v>-0.0571</v>
       </c>
     </row>
     <row r="60">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>-1.6911</v>
+        <v>-11.5272</v>
       </c>
     </row>
     <row r="62">
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0.2827</v>
+        <v>0.2823</v>
       </c>
     </row>
     <row r="63">
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1765</v>
+        <v>0.1981</v>
       </c>
     </row>
     <row r="65">
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.01</v>
+        <v>-0.0002</v>
       </c>
     </row>
     <row r="66">
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>7.4036</v>
+        <v>7.5091</v>
       </c>
     </row>
     <row r="68">
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>-4.137</v>
+        <v>-5.6985</v>
       </c>
     </row>
     <row r="71">
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2483</v>
+        <v>0.2497</v>
       </c>
     </row>
     <row r="75">
@@ -1398,13 +1398,91 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>第26站-other</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>第27站-1</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" t="n">
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>第27站-2</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>第27站-other</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>第28站-1</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>第28站-2</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>第28站-other</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="n">
         <v>0</v>
       </c>
     </row>
